--- a/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
@@ -10,108 +10,6 @@
   </sheets>
   <calcPr fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>TrustCabinet Team</author>
-  </authors>
-  <commentList>
-    <comment ref="B10" authorId="0">
-      <text>
-        <t>Preconditions: Administrator representative; disposable accounts.
-Procedure:
-1. Create user and role.
-2. Assign capabilities.
-3. Deactivate/reactivate.
-4. Confirm permitted work.
-Expected result: Tasks are usable; permissions correct; final administrator protected.
-Source: frontend/src/features/access/UsersPage.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0">
-      <text>
-        <t>Preconditions: Organizer with MeetingCreator.
-Procedure:
-1. Create Draft with schedule/location/content.
-2. Edit.
-3. Find and reopen.
-Expected result: Information persists; organizer confirms form supports preparation.
-Source: frontend/src/features/meetings/MeetingForm.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0">
-      <text>
-        <t>Preconditions: Organizer/approver representatives; ready meetings.
-Procedure:
-1. Submit.
-2. Approve one meeting.
-3. Reject another with reason.
-4. Check feedback.
-Expected result: Parties understand outcomes/reasons; history identifies reviewer.
-Source: frontend/src/features/meetings/workflow/MeetingWorkflowBar.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0">
-      <text>
-        <t>Preconditions: Approved fixture with roster; participant; SMTP sandbox.
-Procedure:
-1. Publish.
-2. Read notification and ICS email.
-3. Open details and Calendar.
-Expected result: Meeting/time/location/content agree across channels.
-Source: frontend/src/features/calendar/CalendarPage.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0">
-      <text>
-        <t>Preconditions: Published meeting; organizer and participant.
-Procedure:
-1. Reschedule.
-2. Find new time through notification and Calendar.
-3. Confirm applicable time.
-Expected result: Participant recognizes latest time without contradictory information.
-Source: frontend/src/features/meetings/MeetingForm.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0">
-      <text>
-        <t>Preconditions: Participant and unrelated-user representatives.
-Procedure:
-1. Open invited meeting.
-2. Search/enter URL as outsider.
-3. Review with administrator.
-Expected result: Participant sees permitted data; outsider cannot view restricted content.
-Source: frontend/src/features/meetings/detail/MeetingDetailPage.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B16" authorId="0">
-      <text>
-        <t>Preconditions: Administrator/user representatives; SMTP sandbox.
-Procedure:
-1. Request reset.
-2. Read email and change password.
-3. Sign in again.
-Expected result: User can follow instructions; consumed link cannot be reused.
-Source: frontend/src/features/auth/LoginPage.tsx</t>
-      </text>
-    </comment>
-    <comment ref="B17" authorId="0">
-      <text>
-        <t>Preconditions: Chrome/Edge; record versions and screen sizes in evidence.
-Procedure:
-1. Sign in.
-2. Find meeting.
-3. Open Calendar.
-4. Read notifications.
-5. Record suggestions.
-Expected result: No UI defect blocks tasks; feedback is recorded separately from acceptance.
-Source: frontend/src/features/meetings/MeetingsPage.tsx</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1270,7 +1168,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="14" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-29</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1298,8 +1196,8 @@
         <v>Document Code</v>
       </c>
       <c r="B6" s="16" t="str">
-        <f>B5&amp;"_"&amp;B2&amp;"_"&amp;F6</f>
-        <v>SEP490-G116_USER ACCEPTANCE TEST REPORT DOCUMENT_1</v>
+        <f>B5&amp;"_"&amp;B2&amp;"_v"&amp;F6</f>
+        <v>SEP490-G116_USER ACCEPTANCE TEST REPORT DOCUMENT_v1.1</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6"/>
@@ -1307,7 +1205,7 @@
         <v>Version</v>
       </c>
       <c r="F6" s="17" t="str">
-        <v>1.0</v>
+        <v>1.1</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -1463,12 +1361,14 @@
       <c r="B11" s="26" t="str">
         <v>1.0</v>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="27" t="str">
+        <v>Report 5</v>
+      </c>
       <c r="D11" s="27" t="str">
         <v>A</v>
       </c>
       <c r="E11" s="27" t="str">
-        <v>Generate English test documentation from TrustCabinet source using the supplied template.</v>
+        <v>Generate test documents from source</v>
       </c>
       <c r="F11" s="28"/>
       <c r="G11" s="29"/>
@@ -1493,12 +1393,22 @@
       <c r="Z11" s="29"/>
     </row>
     <row r="12" ht="21.75" customHeight="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="31"/>
+      <c r="A12" s="30" t="str">
+        <v>2026-10-29</v>
+      </c>
+      <c r="B12" s="26" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C12" s="27" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="D12" s="27" t="str">
+        <v>M</v>
+      </c>
+      <c r="E12" s="27" t="str">
+        <v>Regenerate: 1099 xUnit methods</v>
+      </c>
+      <c r="F12" s="31" t="str"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
@@ -1882,7 +1792,7 @@
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="47" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-29</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>
@@ -1942,9 +1852,7 @@
       <c r="A6" s="43" t="str">
         <v>Notes</v>
       </c>
-      <c r="B6" s="49" t="str">
-        <v>No customer feedback or acceptance decision has been collected. Criteria below require representative-user execution.</v>
-      </c>
+      <c r="B6" s="49" t="str"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6"/>
@@ -2066,7 +1974,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E10" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
@@ -2098,7 +2006,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E11" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
@@ -2130,7 +2038,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E12" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
@@ -2162,7 +2070,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E13" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="39"/>
@@ -2194,7 +2102,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E14" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
@@ -2226,7 +2134,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E15" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
@@ -2258,7 +2166,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E16" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F16" s="39"/>
       <c r="G16" s="39"/>
@@ -2290,7 +2198,7 @@
         <v>No response collected.</v>
       </c>
       <c r="E17" s="63" t="str">
-        <v>NotRun</v>
+        <v>Pending</v>
       </c>
       <c r="F17" s="39"/>
       <c r="G17" s="39"/>
@@ -2495,7 +2403,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
   </mergeCells>
-  <legacyDrawing r:id="noteShapes"/>
 </worksheet>
 </file>
 

--- a/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
@@ -1168,7 +1168,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="14" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="30" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="B12" s="26" t="str">
         <v>1.1</v>
@@ -1406,7 +1406,7 @@
         <v>M</v>
       </c>
       <c r="E12" s="27" t="str">
-        <v>Regenerate: 1099 xUnit methods</v>
+        <v>Regenerate: 1129 xUnit methods</v>
       </c>
       <c r="F12" s="31" t="str"/>
       <c r="G12" s="29"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="47" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40"/>

--- a/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.4_Acceptance_Test.xlsx
@@ -24,92 +24,91 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="26.0"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="20.0"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font/>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF993300"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color rgb="FF008000"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <i/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="20.0"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="MS PGothic"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <color rgb="FF993300"/>
-      <name val="Tahoma"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -129,22 +128,21 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="5">
@@ -866,14 +864,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
